--- a/docs/api-mapping/catatan-dev-team.xlsx
+++ b/docs/api-mapping/catatan-dev-team.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1021"/>
+  <dimension ref="A1:I1021"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="2.63" customWidth="1" style="17" min="1" max="1"/>
@@ -432,7 +432,8 @@
     <col width="23.88" customWidth="1" style="17" min="5" max="5"/>
     <col width="15.75" customWidth="1" style="17" min="6" max="6"/>
     <col width="13" customWidth="1" style="17" min="7" max="7"/>
-    <col width="58" customWidth="1" style="17" min="8" max="8"/>
+    <col width="52" customWidth="1" style="17" min="8" max="8"/>
+    <col width="52" customWidth="1" style="17" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -457,7 +458,12 @@
       </c>
       <c r="H1" s="18" t="inlineStr">
         <is>
-          <t>Endpoint BMKG (hasil scrapping baseline)</t>
+          <t>Endpoint BMKG (path)</t>
+        </is>
+      </c>
+      <c r="I1" s="18" t="inlineStr">
+        <is>
+          <t>Keterangan</t>
         </is>
       </c>
     </row>
@@ -528,7 +534,12 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>GET /api/df/v1/adm/coord (GPS→alamat admin) — sudah dipakai redesign</t>
+          <t>GET /api/df/v1/adm/coord</t>
+        </is>
+      </c>
+      <c r="I4" s="20" t="inlineStr">
+        <is>
+          <t>GPS → alamat admin; sudah dipakai redesign</t>
         </is>
       </c>
     </row>
@@ -561,7 +572,12 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>lokasi.timezone dari /api/df/v1/forecast/coord</t>
+          <t>GET /api/df/v1/forecast/coord</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>field lokasi.timezone (deteksi WIB/WITA/WIT)</t>
         </is>
       </c>
     </row>
@@ -590,7 +606,12 @@
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>GET /api/presentwx/coord (observasi) + /api/df/v1/forecast/coord</t>
+          <t>GET /api/presentwx/coord</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>observasi aktual kartu kondisi saat ini</t>
         </is>
       </c>
     </row>
@@ -616,6 +637,11 @@
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
           <t>Tidak terdeteksi di baseline (form laporan, tanpa XHR)</t>
         </is>
       </c>
@@ -649,6 +675,11 @@
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
           <t>Statis (link App Store/Play Store)</t>
         </is>
       </c>
@@ -682,7 +713,12 @@
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
-          <t>GET /api/df/v1/forecast/coord + /api/presentwx/coord per koordinat kota</t>
+          <t>GET /api/df/v1/forecast/coord + GET /api/presentwx/coord</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>per koordinat kota</t>
         </is>
       </c>
     </row>
@@ -715,6 +751,11 @@
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
           <t>Tidak ada endpoint khusus — dihitung klien dari presentwx (t, hu, ws)</t>
         </is>
       </c>
@@ -748,7 +789,12 @@
       </c>
       <c r="H11" s="20" t="inlineStr">
         <is>
-          <t>Tidak ada JSON AQI — hanya tile polusi /api/v1/spartan/pollution/{pol}/...</t>
+          <t>GET /api/v1/spartan/pollution/{pol}/{lvl}/{t0}/{t1}/{z}/{x}/{y}.png</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>Tidak ada JSON AQI — hanya tile polusi untuk peta</t>
         </is>
       </c>
     </row>
@@ -777,7 +823,12 @@
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>GET /api/presentwx/coord: t (suhu), ws (angin), wd (arah), hu (kelembapan)</t>
+          <t>GET /api/presentwx/coord</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>sumber parameter: t, ws, wd, hu</t>
         </is>
       </c>
     </row>
@@ -803,7 +854,12 @@
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>GET /api/presentwx/coord → t</t>
+          <t>GET /api/presentwx/coord</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>field t (°C)</t>
         </is>
       </c>
     </row>
@@ -829,7 +885,12 @@
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>GET /api/presentwx/coord → ws</t>
+          <t>GET /api/presentwx/coord</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>field ws (km/h)</t>
         </is>
       </c>
     </row>
@@ -855,7 +916,12 @@
       </c>
       <c r="H15" s="20" t="inlineStr">
         <is>
-          <t>GET /api/presentwx/coord → wd / wd_deg</t>
+          <t>GET /api/presentwx/coord</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>field wd / wd_deg</t>
         </is>
       </c>
     </row>
@@ -881,7 +947,12 @@
       </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
-          <t>GET /api/presentwx/coord → hu</t>
+          <t>GET /api/presentwx/coord</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>field hu (%)</t>
         </is>
       </c>
     </row>
@@ -914,6 +985,11 @@
       </c>
       <c r="H17" s="20" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
           <t>Tidak ada (fitur investigasi, tanpa API)</t>
         </is>
       </c>
@@ -943,7 +1019,12 @@
       </c>
       <c r="H18" s="20" t="inlineStr">
         <is>
-          <t>GET /api/df/v1/forecast/coord → data[0].cuaca[0] (hourly)</t>
+          <t>GET /api/df/v1/forecast/coord</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>data[0].cuaca[0] = grup hourly</t>
         </is>
       </c>
     </row>
@@ -969,7 +1050,12 @@
       </c>
       <c r="H19" s="20" t="inlineStr">
         <is>
-          <t>forecast/coord → t per jam</t>
+          <t>GET /api/df/v1/forecast/coord</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>field t per jam</t>
         </is>
       </c>
     </row>
@@ -995,7 +1081,12 @@
       </c>
       <c r="H20" s="20" t="inlineStr">
         <is>
-          <t>forecast/coord → tp (mm) per jam</t>
+          <t>GET /api/df/v1/forecast/coord</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>field tp (mm) per jam</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1112,12 @@
       </c>
       <c r="H21" s="20" t="inlineStr">
         <is>
-          <t>forecast/coord → ws per jam</t>
+          <t>GET /api/df/v1/forecast/coord</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>field ws per jam</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1143,12 @@
       </c>
       <c r="H22" s="20" t="inlineStr">
         <is>
-          <t>forecast/coord → hu per jam</t>
+          <t>GET /api/df/v1/forecast/coord</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>field hu per jam</t>
         </is>
       </c>
     </row>
@@ -1073,6 +1174,11 @@
       </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
           <t>Tidak ada JSON AQ per jam (hanya tile polusi)</t>
         </is>
       </c>
@@ -1101,6 +1207,11 @@
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>Lihat per sub-aktivitas</t>
         </is>
@@ -1128,6 +1239,11 @@
       </c>
       <c r="H25" s="20" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
           <t>Tidak terdeteksi di baseline (redesign pakai Overpass OSM)</t>
         </is>
       </c>
@@ -1154,7 +1270,12 @@
       </c>
       <c r="H26" s="20" t="inlineStr">
         <is>
-          <t>/api/v1/public/maritim/nearest-location (wilayah laut terdekat)</t>
+          <t>GET /api/v1/public/maritim/nearest-location</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>wilayah laut terdekat (code, name, wilpel, polygon)</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1301,12 @@
       </c>
       <c r="H27" s="20" t="inlineStr">
         <is>
-          <t>/api/v1/maritim/route + /api/v1/maritim/water-area + nearest-location</t>
+          <t>GET /api/v1/maritim/route + /api/v1/maritim/water-area/water_area_point.geojson</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>rute pelayaran + titik area laut</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1332,12 @@
       </c>
       <c r="H28" s="20" t="inlineStr">
         <is>
-          <t>/api/v1/maps/aviation/metadata/tiles + /api/v1/sus/modelrun</t>
+          <t>GET /api/v1/maps/aviation/metadata/tiles + GET /api/v1/sus/modelrun</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>layer peta penerbangan + katalog run model</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1366,12 @@
       </c>
       <c r="H29" s="20" t="inlineStr">
         <is>
-          <t>widis.bmkg.go.id/ndf/cgms (perlu reverse param) + inderaja HIMA (statis)</t>
+          <t>GET widis.bmkg.go.id/ndf/cgms/weather/forward</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>perlu reverse-engineering param; alternatif statis: inderaja HIMA</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1397,12 @@
       </c>
       <c r="H30" s="20" t="inlineStr">
         <is>
-          <t>Sama seperti r29 — belum ada endpoint JSON terdokumentasi</t>
+          <t>GET widis.bmkg.go.id/ndf/cgms/weather/forward</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
+        <is>
+          <t>belum ada endpoint JSON terdokumentasi</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1428,12 @@
       </c>
       <c r="H31" s="20" t="inlineStr">
         <is>
-          <t>Sama seperti r29 — citra awan via HIMA/widis</t>
+          <t>GET widis.bmkg.go.id/ndf/cgms/weather/forward</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>citra awan via HIMA/widis</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1459,12 @@
       </c>
       <c r="H32" s="20" t="inlineStr">
         <is>
-          <t>Tile QPE via spartan modelrun catalog (gsmap/QPE24h)</t>
+          <t>spartan.bmkg.go.id/map/modelrun (katalog QPE/gsmap)</t>
+        </is>
+      </c>
+      <c r="I32" s="20" t="inlineStr">
+        <is>
+          <t>tile curah hujan satelit</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1490,12 @@
       </c>
       <c r="H33" s="20" t="inlineStr">
         <is>
-          <t>https://bmkg-sus.geo.id/windmap/ecmwf (wind tiles) + modelrun</t>
+          <t>GET bmkg-sus.geo.id/windmap/ecmwf</t>
+        </is>
+      </c>
+      <c r="I33" s="20" t="inlineStr">
+        <is>
+          <t>wind tiles ECMWF</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1528,12 @@
       </c>
       <c r="H34" s="20" t="inlineStr">
         <is>
-          <t>/api/v1/maps/{general,warning,maritim,aviation,tourism}/metadata/tiles</t>
+          <t>GET /api/v1/maps/{general,warning,maritim,aviation,tourism}/metadata/tiles</t>
+        </is>
+      </c>
+      <c r="I34" s="20" t="inlineStr">
+        <is>
+          <t>metadata layer peta (sources, layers, overlays)</t>
         </is>
       </c>
     </row>
@@ -1405,6 +1566,11 @@
       </c>
       <c r="H35" s="20" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" s="20" t="inlineStr">
+        <is>
           <t>Tidak ada di cuaca.bmkg.go.id (redesign pakai data.bmkg.go.id TEWS — legacy)</t>
         </is>
       </c>
@@ -1438,6 +1604,11 @@
       </c>
       <c r="H36" s="20" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" s="20" t="inlineStr">
+        <is>
           <t>Tidak ada (original redirect ke signature.bmkg.go.id/dwt)</t>
         </is>
       </c>
@@ -1462,6 +1633,11 @@
         </is>
       </c>
       <c r="H37" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" s="20" t="inlineStr">
         <is>
           <t>Konten statis</t>
         </is>

--- a/docs/api-mapping/catatan-dev-team.xlsx
+++ b/docs/api-mapping/catatan-dev-team.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>GET /api/df/v1/adm/coord</t>
+          <t>GET https://cuaca.bmkg.go.id/api/df/v1/adm/coord</t>
         </is>
       </c>
       <c r="I4" s="20" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>GET /api/df/v1/forecast/coord</t>
+          <t>GET https://cuaca.bmkg.go.id/api/df/v1/forecast/coord</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>GET /api/presentwx/coord</t>
+          <t>GET https://cuaca.bmkg.go.id/api/presentwx/coord</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
-          <t>GET /api/df/v1/forecast/coord + GET /api/presentwx/coord</t>
+          <t>GET https://cuaca.bmkg.go.id/api/df/v1/forecast/coord , GET https://cuaca.bmkg.go.id/api/presentwx/coord</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="H11" s="20" t="inlineStr">
         <is>
-          <t>GET /api/v1/spartan/pollution/{pol}/{lvl}/{t0}/{t1}/{z}/{x}/{y}.png</t>
+          <t>GET https://cuaca.bmkg.go.id/api/v1/spartan/pollution/{pol}/{lvl}/{t0}/{t1}/{z}/{x}/{y}.png</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>GET /api/presentwx/coord</t>
+          <t>GET https://cuaca.bmkg.go.id/api/presentwx/coord</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>GET /api/presentwx/coord</t>
+          <t>GET https://cuaca.bmkg.go.id/api/presentwx/coord</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>GET /api/presentwx/coord</t>
+          <t>GET https://cuaca.bmkg.go.id/api/presentwx/coord</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="H15" s="20" t="inlineStr">
         <is>
-          <t>GET /api/presentwx/coord</t>
+          <t>GET https://cuaca.bmkg.go.id/api/presentwx/coord</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
-          <t>GET /api/presentwx/coord</t>
+          <t>GET https://cuaca.bmkg.go.id/api/presentwx/coord</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H18" s="20" t="inlineStr">
         <is>
-          <t>GET /api/df/v1/forecast/coord</t>
+          <t>GET https://cuaca.bmkg.go.id/api/df/v1/forecast/coord</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="H19" s="20" t="inlineStr">
         <is>
-          <t>GET /api/df/v1/forecast/coord</t>
+          <t>GET https://cuaca.bmkg.go.id/api/df/v1/forecast/coord</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H20" s="20" t="inlineStr">
         <is>
-          <t>GET /api/df/v1/forecast/coord</t>
+          <t>GET https://cuaca.bmkg.go.id/api/df/v1/forecast/coord</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="H21" s="20" t="inlineStr">
         <is>
-          <t>GET /api/df/v1/forecast/coord</t>
+          <t>GET https://cuaca.bmkg.go.id/api/df/v1/forecast/coord</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="H22" s="20" t="inlineStr">
         <is>
-          <t>GET /api/df/v1/forecast/coord</t>
+          <t>GET https://cuaca.bmkg.go.id/api/df/v1/forecast/coord</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="H26" s="20" t="inlineStr">
         <is>
-          <t>GET /api/v1/public/maritim/nearest-location</t>
+          <t>GET https://cuaca.bmkg.go.id/api/v1/public/maritim/nearest-location</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H27" s="20" t="inlineStr">
         <is>
-          <t>GET /api/v1/maritim/route + /api/v1/maritim/water-area/water_area_point.geojson</t>
+          <t>GET https://cuaca.bmkg.go.id/api/v1/maritim/route , https://cuaca.bmkg.go.id/api/v1/maritim/water-area/water_area_point.geojson</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="H28" s="20" t="inlineStr">
         <is>
-          <t>GET /api/v1/maps/aviation/metadata/tiles + GET /api/v1/sus/modelrun</t>
+          <t>GET https://cuaca.bmkg.go.id/api/v1/maps/aviation/metadata/tiles , GET https://cuaca.bmkg.go.id/api/v1/sus/modelrun</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="H34" s="20" t="inlineStr">
         <is>
-          <t>GET /api/v1/maps/{general,warning,maritim,aviation,tourism}/metadata/tiles</t>
+          <t>GET https://cuaca.bmkg.go.id/api/v1/maps/{general,warning,maritim,aviation,tourism}/metadata/tiles</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr">

--- a/docs/api-mapping/catatan-dev-team.xlsx
+++ b/docs/api-mapping/catatan-dev-team.xlsx
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H29" s="20" t="inlineStr">
         <is>
-          <t>GET widis.bmkg.go.id/ndf/cgms/weather/forward</t>
+          <t>GET https://widis.bmkg.go.id/ndf/cgms/weather/forward</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="H32" s="20" t="inlineStr">
         <is>
-          <t>spartan.bmkg.go.id/map/modelrun (katalog QPE/gsmap)</t>
+          <t>GET https://spartan.bmkg.go.id/map/modelrun (katalog QPE/gsmap)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="H33" s="20" t="inlineStr">
         <is>
-          <t>GET bmkg-sus.geo.id/windmap/ecmwf</t>
+          <t>GET https://bmkg-sus.geo.id/windmap/ecmwf</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">

--- a/docs/api-mapping/catatan-dev-team.xlsx
+++ b/docs/api-mapping/catatan-dev-team.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -56,8 +56,16 @@
       <b val="1"/>
       <color rgb="007F6000"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -84,6 +92,16 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -91,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -147,6 +165,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -422,7 +443,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1021"/>
+  <dimension ref="A1:J1021"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="2.63" customWidth="1" style="17" min="1" max="1"/>
@@ -434,6 +455,7 @@
     <col width="13" customWidth="1" style="17" min="7" max="7"/>
     <col width="52" customWidth="1" style="17" min="8" max="8"/>
     <col width="52" customWidth="1" style="17" min="9" max="9"/>
+    <col width="13" customWidth="1" style="17" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,6 +488,11 @@
           <t>Keterangan</t>
         </is>
       </c>
+      <c r="J1" s="18" t="inlineStr">
+        <is>
+          <t>Akses di Dev</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
@@ -542,6 +569,11 @@
           <t>GPS → alamat admin; sudah dipakai redesign</t>
         </is>
       </c>
+      <c r="J4" s="23" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="n"/>
@@ -580,6 +612,11 @@
           <t>field lokasi.timezone (deteksi WIB/WITA/WIT)</t>
         </is>
       </c>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="n"/>
@@ -612,6 +649,11 @@
       <c r="I6" s="20" t="inlineStr">
         <is>
           <t>observasi aktual kartu kondisi saat ini</t>
+        </is>
+      </c>
+      <c r="J6" s="24" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
         </is>
       </c>
     </row>
@@ -645,6 +687,11 @@
           <t>Tidak terdeteksi di baseline (form laporan, tanpa XHR)</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="n"/>
@@ -683,6 +730,11 @@
           <t>Statis (link App Store/Play Store)</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="n"/>
@@ -721,6 +773,11 @@
           <t>per koordinat kota</t>
         </is>
       </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="n"/>
@@ -759,6 +816,11 @@
           <t>Tidak ada endpoint khusus — dihitung klien dari presentwx (t, hu, ws)</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="n"/>
@@ -797,6 +859,11 @@
           <t>Tidak ada JSON AQI — hanya tile polusi untuk peta</t>
         </is>
       </c>
+      <c r="J11" s="24" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="n"/>
@@ -829,6 +896,11 @@
       <c r="I12" s="20" t="inlineStr">
         <is>
           <t>sumber parameter: t, ws, wd, hu</t>
+        </is>
+      </c>
+      <c r="J12" s="24" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
         </is>
       </c>
     </row>
@@ -862,6 +934,11 @@
           <t>field t (°C)</t>
         </is>
       </c>
+      <c r="J13" s="24" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="n"/>
@@ -893,6 +970,11 @@
           <t>field ws (km/h)</t>
         </is>
       </c>
+      <c r="J14" s="24" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="n"/>
@@ -924,6 +1006,11 @@
           <t>field wd / wd_deg</t>
         </is>
       </c>
+      <c r="J15" s="24" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="n"/>
@@ -955,6 +1042,11 @@
           <t>field hu (%)</t>
         </is>
       </c>
+      <c r="J16" s="24" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="n"/>
@@ -993,6 +1085,11 @@
           <t>Tidak ada (fitur investigasi, tanpa API)</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="n"/>
@@ -1025,6 +1122,11 @@
       <c r="I18" s="20" t="inlineStr">
         <is>
           <t>data[0].cuaca[0] = grup hourly</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="inlineStr">
+        <is>
+          <t>PROXY</t>
         </is>
       </c>
     </row>
@@ -1058,6 +1160,11 @@
           <t>field t per jam</t>
         </is>
       </c>
+      <c r="J19" s="23" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="n"/>
@@ -1089,6 +1196,11 @@
           <t>field tp (mm) per jam</t>
         </is>
       </c>
+      <c r="J20" s="23" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="n"/>
@@ -1120,6 +1232,11 @@
           <t>field ws per jam</t>
         </is>
       </c>
+      <c r="J21" s="23" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="n"/>
@@ -1151,6 +1268,11 @@
           <t>field hu per jam</t>
         </is>
       </c>
+      <c r="J22" s="23" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="n"/>
@@ -1182,6 +1304,11 @@
           <t>Tidak ada JSON AQ per jam (hanya tile polusi)</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="n"/>
@@ -1214,6 +1341,11 @@
       <c r="I24" s="20" t="inlineStr">
         <is>
           <t>Lihat per sub-aktivitas</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1247,6 +1379,11 @@
           <t>Tidak terdeteksi di baseline (redesign pakai Overpass OSM)</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="n"/>
@@ -1278,6 +1415,11 @@
           <t>wilayah laut terdekat (code, name, wilpel, polygon)</t>
         </is>
       </c>
+      <c r="J26" s="23" t="inlineStr">
+        <is>
+          <t>PROXY</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="n"/>
@@ -1309,6 +1451,11 @@
           <t>rute pelayaran + titik area laut</t>
         </is>
       </c>
+      <c r="J27" s="24" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="n"/>
@@ -1340,6 +1487,11 @@
           <t>layer peta penerbangan + katalog run model</t>
         </is>
       </c>
+      <c r="J28" s="24" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="n"/>
@@ -1372,6 +1524,11 @@
       <c r="I29" s="20" t="inlineStr">
         <is>
           <t>perlu reverse-engineering param; alternatif statis: inderaja HIMA</t>
+        </is>
+      </c>
+      <c r="J29" s="24" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
         </is>
       </c>
     </row>
@@ -1405,6 +1562,11 @@
           <t>belum ada endpoint JSON terdokumentasi</t>
         </is>
       </c>
+      <c r="J30" s="24" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="n"/>
@@ -1436,6 +1598,11 @@
           <t>citra awan via HIMA/widis</t>
         </is>
       </c>
+      <c r="J31" s="24" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="n"/>
@@ -1467,6 +1634,11 @@
           <t>tile curah hujan satelit</t>
         </is>
       </c>
+      <c r="J32" s="24" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="n"/>
@@ -1498,6 +1670,11 @@
           <t>wind tiles ECMWF</t>
         </is>
       </c>
+      <c r="J33" s="24" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="n"/>
@@ -1536,6 +1713,11 @@
           <t>metadata layer peta (sources, layers, overlays)</t>
         </is>
       </c>
+      <c r="J34" s="24" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="13" t="n"/>
@@ -1574,6 +1756,11 @@
           <t>Tidak ada di cuaca.bmkg.go.id (redesign pakai data.bmkg.go.id TEWS — legacy)</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="n"/>
@@ -1612,6 +1799,11 @@
           <t>Tidak ada (original redirect ke signature.bmkg.go.id/dwt)</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="13" t="n"/>
@@ -1640,6 +1832,11 @@
       <c r="I37" s="20" t="inlineStr">
         <is>
           <t>Konten statis</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1752,6 +1949,11 @@
       <c r="C47" s="16" t="n"/>
       <c r="D47" s="14" t="n"/>
       <c r="F47" s="12" t="n"/>
+      <c r="I47" s="25" t="inlineStr">
+        <is>
+          <t>Keterangan kolom "Akses di Dev":</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="n"/>
@@ -1759,6 +1961,11 @@
       <c r="C48" s="16" t="n"/>
       <c r="D48" s="14" t="n"/>
       <c r="F48" s="12" t="n"/>
+      <c r="I48" s="20" t="inlineStr">
+        <is>
+          <t>PROXY = wajib lewat proxy server dev (vite) karena server BMKG menolak request browser langsung (cek header Referer/Origin). DIRECT = browser bisa panggil langsung (URL https://cuaca.bmkg.go.id tampil penuh di devtools).</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="13" t="n"/>
